--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>Result</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>Thu Jul 09 18:09:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:35:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:37:06 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -640,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -656,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -674,7 +683,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
